--- a/outputs/tables/descriptive_statistics.xlsx
+++ b/outputs/tables/descriptive_statistics.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>missing_pct_preimp</t>
+          <t>missing_pct_recorded</t>
         </is>
       </c>
     </row>
@@ -496,34 +496,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E2" t="n">
-        <v>66.227</v>
+        <v>66.797</v>
       </c>
       <c r="F2" t="n">
-        <v>40.472</v>
+        <v>42.544</v>
       </c>
       <c r="G2" t="n">
         <v>-533.58</v>
       </c>
       <c r="H2" t="n">
-        <v>53.5</v>
+        <v>53.283</v>
       </c>
       <c r="I2" t="n">
-        <v>62.319</v>
+        <v>62.291</v>
       </c>
       <c r="J2" t="n">
-        <v>71.97799999999999</v>
+        <v>72.458</v>
       </c>
       <c r="K2" t="n">
         <v>944.1660000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>8.423999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>5.144</v>
+        <v>0.545</v>
       </c>
     </row>
     <row r="3">
@@ -543,34 +543,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E3" t="n">
-        <v>36064.7</v>
+        <v>36286.257</v>
       </c>
       <c r="F3" t="n">
-        <v>89092.76700000001</v>
+        <v>89593.56299999999</v>
       </c>
       <c r="G3" t="n">
         <v>0.02</v>
       </c>
       <c r="H3" t="n">
-        <v>1614.482</v>
+        <v>1524.919</v>
       </c>
       <c r="I3" t="n">
-        <v>7026.024</v>
+        <v>6996.604</v>
       </c>
       <c r="J3" t="n">
-        <v>20168.49</v>
+        <v>20584.588</v>
       </c>
       <c r="K3" t="n">
         <v>879001</v>
       </c>
       <c r="L3" t="n">
-        <v>4.55</v>
+        <v>4.589</v>
       </c>
       <c r="M3" t="n">
-        <v>5.166</v>
+        <v>0.454</v>
       </c>
     </row>
     <row r="4">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E4" t="n">
-        <v>13170.29</v>
+        <v>13256.738</v>
       </c>
       <c r="F4" t="n">
-        <v>38371.127</v>
+        <v>38113.516</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>303.986</v>
+        <v>265.027</v>
       </c>
       <c r="I4" t="n">
-        <v>1817.179</v>
+        <v>1796</v>
       </c>
       <c r="J4" t="n">
-        <v>7088.228</v>
+        <v>7336.804</v>
       </c>
       <c r="K4" t="n">
         <v>567647</v>
       </c>
       <c r="L4" t="n">
-        <v>5.933</v>
+        <v>5.761</v>
       </c>
       <c r="M4" t="n">
-        <v>6.78</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="5">
@@ -637,34 +637,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4415</v>
+        <v>4389</v>
       </c>
       <c r="E5" t="n">
-        <v>902.024</v>
+        <v>886.859</v>
       </c>
       <c r="F5" t="n">
-        <v>2593.487</v>
+        <v>2585.007</v>
       </c>
       <c r="G5" t="n">
         <v>-2234</v>
       </c>
       <c r="H5" t="n">
-        <v>53.424</v>
+        <v>52.802</v>
       </c>
       <c r="I5" t="n">
-        <v>176.773</v>
+        <v>174.949</v>
       </c>
       <c r="J5" t="n">
-        <v>478.812</v>
+        <v>468.985</v>
       </c>
       <c r="K5" t="n">
         <v>34296</v>
       </c>
       <c r="L5" t="n">
-        <v>6.24</v>
+        <v>6.331</v>
       </c>
       <c r="M5" t="n">
-        <v>4.972</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="6">
@@ -684,34 +684,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4415</v>
+        <v>4389</v>
       </c>
       <c r="E6" t="n">
-        <v>2.004</v>
+        <v>2.006</v>
       </c>
       <c r="F6" t="n">
-        <v>1.939</v>
+        <v>1.944</v>
       </c>
       <c r="G6" t="n">
         <v>-62.425</v>
       </c>
       <c r="H6" t="n">
-        <v>1.164</v>
+        <v>1.161</v>
       </c>
       <c r="I6" t="n">
-        <v>1.68</v>
+        <v>1.684</v>
       </c>
       <c r="J6" t="n">
-        <v>2.599</v>
+        <v>2.603</v>
       </c>
       <c r="K6" t="n">
         <v>22.725</v>
       </c>
       <c r="L6" t="n">
-        <v>-6.544</v>
+        <v>-6.534</v>
       </c>
       <c r="M6" t="n">
-        <v>4.972</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="7">
@@ -731,34 +731,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4429</v>
+        <v>4403</v>
       </c>
       <c r="E7" t="n">
-        <v>1652.433</v>
+        <v>1634.761</v>
       </c>
       <c r="F7" t="n">
-        <v>4673.055</v>
+        <v>4672.798</v>
       </c>
       <c r="G7" t="n">
         <v>-3338</v>
       </c>
       <c r="H7" t="n">
-        <v>110.694</v>
+        <v>110.26</v>
       </c>
       <c r="I7" t="n">
-        <v>337.739</v>
+        <v>336.426</v>
       </c>
       <c r="J7" t="n">
-        <v>912.768</v>
+        <v>893.457</v>
       </c>
       <c r="K7" t="n">
         <v>50321</v>
       </c>
       <c r="L7" t="n">
-        <v>5.727</v>
+        <v>5.765</v>
       </c>
       <c r="M7" t="n">
-        <v>4.671</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="8">
@@ -778,34 +778,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4623</v>
+        <v>4402</v>
       </c>
       <c r="E8" t="n">
-        <v>0.417</v>
+        <v>0.386</v>
       </c>
       <c r="F8" t="n">
-        <v>3.126</v>
+        <v>2.866</v>
       </c>
       <c r="G8" t="n">
         <v>-76.48</v>
       </c>
       <c r="H8" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="I8" t="n">
-        <v>0.52</v>
+        <v>0.523</v>
       </c>
       <c r="J8" t="n">
-        <v>0.959</v>
+        <v>0.946</v>
       </c>
       <c r="K8" t="n">
-        <v>54.395</v>
+        <v>23.572</v>
       </c>
       <c r="L8" t="n">
-        <v>-7.798</v>
+        <v>-12.171</v>
       </c>
       <c r="M8" t="n">
-        <v>0.495</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="9">
@@ -825,34 +825,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4599</v>
+        <v>4384</v>
       </c>
       <c r="E9" t="n">
-        <v>3.275</v>
+        <v>3.687</v>
       </c>
       <c r="F9" t="n">
-        <v>32.703</v>
+        <v>27.948</v>
       </c>
       <c r="G9" t="n">
-        <v>-914.7859999999999</v>
+        <v>-845.864</v>
       </c>
       <c r="H9" t="n">
-        <v>3.106</v>
+        <v>3.27</v>
       </c>
       <c r="I9" t="n">
-        <v>6.073</v>
+        <v>6.104</v>
       </c>
       <c r="J9" t="n">
-        <v>10.45</v>
+        <v>10.469</v>
       </c>
       <c r="K9" t="n">
-        <v>349.958</v>
+        <v>98.907</v>
       </c>
       <c r="L9" t="n">
-        <v>-14.173</v>
+        <v>-14.414</v>
       </c>
       <c r="M9" t="n">
-        <v>1.012</v>
+        <v>0.477</v>
       </c>
     </row>
     <row r="10">
@@ -872,34 +872,34 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E10" t="n">
-        <v>27480.224</v>
+        <v>27570.343</v>
       </c>
       <c r="F10" t="n">
-        <v>74695.55899999999</v>
+        <v>75332.40300000001</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1618.62</v>
+        <v>1533.647</v>
       </c>
       <c r="I10" t="n">
-        <v>4417.645</v>
+        <v>4396.682</v>
       </c>
       <c r="J10" t="n">
-        <v>15016.208</v>
+        <v>15104.469</v>
       </c>
       <c r="K10" t="n">
         <v>763595</v>
       </c>
       <c r="L10" t="n">
-        <v>5.037</v>
+        <v>5.077</v>
       </c>
       <c r="M10" t="n">
-        <v>6.285</v>
+        <v>1.748</v>
       </c>
     </row>
     <row r="11">
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4414</v>
+        <v>4389</v>
       </c>
       <c r="E11" t="n">
-        <v>0.101</v>
+        <v>0.102</v>
       </c>
       <c r="F11" t="n">
         <v>0.081</v>
@@ -943,10 +943,10 @@
         <v>0.956</v>
       </c>
       <c r="L11" t="n">
-        <v>4.819</v>
+        <v>4.824</v>
       </c>
       <c r="M11" t="n">
-        <v>4.994</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="12">
@@ -966,34 +966,34 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4645</v>
+        <v>4404</v>
       </c>
       <c r="E12" t="n">
-        <v>9.176</v>
+        <v>9.315</v>
       </c>
       <c r="F12" t="n">
-        <v>2.205</v>
+        <v>2.005</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.127</v>
+        <v>1.361</v>
       </c>
       <c r="H12" t="n">
-        <v>7.907</v>
+        <v>8.083</v>
       </c>
       <c r="I12" t="n">
-        <v>9.218</v>
+        <v>9.266</v>
       </c>
       <c r="J12" t="n">
-        <v>10.418</v>
+        <v>10.435</v>
       </c>
       <c r="K12" t="n">
         <v>14.605</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.283</v>
+        <v>0.04</v>
       </c>
       <c r="M12" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="13">
@@ -1013,34 +1013,34 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E13" t="n">
-        <v>8.648999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>2.223</v>
+        <v>2.265</v>
       </c>
       <c r="G13" t="n">
         <v>-3.912</v>
       </c>
       <c r="H13" t="n">
-        <v>7.367</v>
+        <v>7.33</v>
       </c>
       <c r="I13" t="n">
-        <v>8.843999999999999</v>
+        <v>8.853</v>
       </c>
       <c r="J13" t="n">
-        <v>9.903</v>
+        <v>9.932</v>
       </c>
       <c r="K13" t="n">
         <v>13.687</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.708</v>
+        <v>-0.715</v>
       </c>
       <c r="M13" t="n">
-        <v>5.166</v>
+        <v>0.454</v>
       </c>
     </row>
     <row r="14">
@@ -1060,34 +1060,34 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E14" t="n">
-        <v>0.605</v>
+        <v>0.604</v>
       </c>
       <c r="F14" t="n">
-        <v>0.274</v>
+        <v>0.286</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.488</v>
+        <v>0.478</v>
       </c>
       <c r="I14" t="n">
-        <v>0.66</v>
+        <v>0.661</v>
       </c>
       <c r="J14" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
       <c r="K14" t="n">
         <v>8.943</v>
       </c>
       <c r="L14" t="n">
-        <v>6.788</v>
+        <v>7.032</v>
       </c>
       <c r="M14" t="n">
-        <v>5.166</v>
+        <v>0.454</v>
       </c>
     </row>
     <row r="15">
@@ -1107,34 +1107,34 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.251</v>
+        <v>0.255</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.357</v>
+        <v>0.352</v>
       </c>
       <c r="I15" t="n">
-        <v>0.601</v>
+        <v>0.596</v>
       </c>
       <c r="J15" t="n">
-        <v>0.771</v>
+        <v>0.772</v>
       </c>
       <c r="K15" t="n">
         <v>0.999</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.296</v>
+        <v>-0.293</v>
       </c>
       <c r="M15" t="n">
-        <v>6.285</v>
+        <v>1.748</v>
       </c>
     </row>
     <row r="16">
@@ -1154,34 +1154,34 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E16" t="n">
-        <v>13.971</v>
+        <v>13.951</v>
       </c>
       <c r="F16" t="n">
-        <v>9.284000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="G16" t="n">
         <v>1.046</v>
       </c>
       <c r="H16" t="n">
-        <v>8.331</v>
+        <v>8.192</v>
       </c>
       <c r="I16" t="n">
-        <v>11.583</v>
+        <v>11.549</v>
       </c>
       <c r="J16" t="n">
-        <v>16.527</v>
+        <v>16.628</v>
       </c>
       <c r="K16" t="n">
         <v>99.232</v>
       </c>
       <c r="L16" t="n">
-        <v>2.773</v>
+        <v>2.643</v>
       </c>
       <c r="M16" t="n">
-        <v>5.273</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="17">
@@ -1201,31 +1201,31 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E17" t="n">
-        <v>1.983</v>
+        <v>1.957</v>
       </c>
       <c r="F17" t="n">
-        <v>3.948</v>
+        <v>3.97</v>
       </c>
       <c r="G17" t="n">
         <v>-16.04</v>
       </c>
       <c r="H17" t="n">
-        <v>0.648</v>
+        <v>0.548</v>
       </c>
       <c r="I17" t="n">
-        <v>2.149</v>
+        <v>2.121</v>
       </c>
       <c r="J17" t="n">
-        <v>3.765</v>
+        <v>3.762</v>
       </c>
       <c r="K17" t="n">
         <v>24.616</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.277</v>
+        <v>-0.26</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1248,31 +1248,31 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E18" t="n">
-        <v>5.442</v>
+        <v>5.431</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4</v>
+        <v>1.407</v>
       </c>
       <c r="G18" t="n">
         <v>2.648</v>
       </c>
       <c r="H18" t="n">
-        <v>4.092</v>
+        <v>4.09</v>
       </c>
       <c r="I18" t="n">
-        <v>5.471</v>
+        <v>5.466</v>
       </c>
       <c r="J18" t="n">
-        <v>6.243</v>
+        <v>6.23</v>
       </c>
       <c r="K18" t="n">
         <v>8.286</v>
       </c>
       <c r="L18" t="n">
-        <v>0.173</v>
+        <v>0.191</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1295,31 +1295,31 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E19" t="n">
-        <v>2.147</v>
+        <v>2.148</v>
       </c>
       <c r="F19" t="n">
-        <v>2.178</v>
+        <v>2.192</v>
       </c>
       <c r="G19" t="n">
         <v>-1.676</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.862</v>
+        <v>1.867</v>
       </c>
       <c r="J19" t="n">
-        <v>3.07</v>
+        <v>3.118</v>
       </c>
       <c r="K19" t="n">
         <v>15.253</v>
       </c>
       <c r="L19" t="n">
-        <v>1.783</v>
+        <v>1.774</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1342,31 +1342,31 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E20" t="n">
-        <v>9.367000000000001</v>
+        <v>9.375</v>
       </c>
       <c r="F20" t="n">
-        <v>4.5</v>
+        <v>4.529</v>
       </c>
       <c r="G20" t="n">
         <v>2.65</v>
       </c>
       <c r="H20" t="n">
-        <v>6.325</v>
+        <v>6.269</v>
       </c>
       <c r="I20" t="n">
         <v>8.324</v>
       </c>
       <c r="J20" t="n">
-        <v>10.718</v>
+        <v>10.737</v>
       </c>
       <c r="K20" t="n">
         <v>27.475</v>
       </c>
       <c r="L20" t="n">
-        <v>1.594</v>
+        <v>1.583</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1389,31 +1389,31 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.671</v>
+        <v>-0.699</v>
       </c>
       <c r="F21" t="n">
-        <v>5.787</v>
+        <v>5.785</v>
       </c>
       <c r="G21" t="n">
         <v>-23.892</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.318</v>
+        <v>-3.264</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.032</v>
+        <v>-0.081</v>
       </c>
       <c r="J21" t="n">
-        <v>2.958</v>
+        <v>2.875</v>
       </c>
       <c r="K21" t="n">
         <v>8.907</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.988</v>
+        <v>-1.001</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1436,31 +1436,31 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E22" t="n">
-        <v>101.744</v>
+        <v>101.646</v>
       </c>
       <c r="F22" t="n">
-        <v>7.833</v>
+        <v>7.755</v>
       </c>
       <c r="G22" t="n">
         <v>75.367</v>
       </c>
       <c r="H22" t="n">
-        <v>97.798</v>
+        <v>97.782</v>
       </c>
       <c r="I22" t="n">
-        <v>101.089</v>
+        <v>100.959</v>
       </c>
       <c r="J22" t="n">
-        <v>105.264</v>
+        <v>105.246</v>
       </c>
       <c r="K22" t="n">
         <v>127.329</v>
       </c>
       <c r="L22" t="n">
-        <v>0.266</v>
+        <v>0.209</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1483,31 +1483,31 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E23" t="n">
-        <v>8.847</v>
+        <v>8.849</v>
       </c>
       <c r="F23" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="G23" t="n">
         <v>1.205</v>
       </c>
       <c r="H23" t="n">
-        <v>8.002000000000001</v>
+        <v>7.98</v>
       </c>
       <c r="I23" t="n">
-        <v>9.183999999999999</v>
+        <v>9.186</v>
       </c>
       <c r="J23" t="n">
-        <v>10.473</v>
+        <v>10.48</v>
       </c>
       <c r="K23" t="n">
         <v>11.895</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.103</v>
+        <v>-1.102</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E24" t="n">
         <v>0.001</v>
@@ -1542,7 +1542,7 @@
         <v>-0.156</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.015</v>
+        <v>-0.014</v>
       </c>
       <c r="I24" t="n">
         <v>0.004</v>
@@ -1554,10 +1554,10 @@
         <v>0.176</v>
       </c>
       <c r="L24" t="n">
-        <v>0.659</v>
+        <v>0.65</v>
       </c>
       <c r="M24" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1577,19 +1577,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E25" t="n">
-        <v>0.273</v>
+        <v>0.27</v>
       </c>
       <c r="F25" t="n">
-        <v>2.693</v>
+        <v>2.685</v>
       </c>
       <c r="G25" t="n">
         <v>-0.997</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.053</v>
+        <v>-0.054</v>
       </c>
       <c r="I25" t="n">
         <v>0.034</v>
@@ -1601,10 +1601,10 @@
         <v>46.744</v>
       </c>
       <c r="L25" t="n">
-        <v>16.167</v>
+        <v>16.214</v>
       </c>
       <c r="M25" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>missing_pct_preimp</t>
+          <t>missing_pct_recorded</t>
         </is>
       </c>
     </row>
@@ -1700,34 +1700,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E2" t="n">
-        <v>66.619</v>
+        <v>66.797</v>
       </c>
       <c r="F2" t="n">
-        <v>41.629</v>
+        <v>42.544</v>
       </c>
       <c r="G2" t="n">
         <v>-533.58</v>
       </c>
       <c r="H2" t="n">
-        <v>53.682</v>
+        <v>53.283</v>
       </c>
       <c r="I2" t="n">
-        <v>62.238</v>
+        <v>62.291</v>
       </c>
       <c r="J2" t="n">
-        <v>71.913</v>
+        <v>72.458</v>
       </c>
       <c r="K2" t="n">
         <v>944.1660000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>8.33</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>5.144</v>
+        <v>0.545</v>
       </c>
     </row>
     <row r="3">
@@ -1747,34 +1747,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E3" t="n">
-        <v>35539.318</v>
+        <v>36286.257</v>
       </c>
       <c r="F3" t="n">
-        <v>88073.967</v>
+        <v>89593.56299999999</v>
       </c>
       <c r="G3" t="n">
         <v>0.02</v>
       </c>
       <c r="H3" t="n">
-        <v>1666.586</v>
+        <v>1524.919</v>
       </c>
       <c r="I3" t="n">
-        <v>7063.845</v>
+        <v>6996.604</v>
       </c>
       <c r="J3" t="n">
-        <v>19900.468</v>
+        <v>20584.588</v>
       </c>
       <c r="K3" t="n">
         <v>879001</v>
       </c>
       <c r="L3" t="n">
-        <v>4.64</v>
+        <v>4.589</v>
       </c>
       <c r="M3" t="n">
-        <v>5.166</v>
+        <v>0.454</v>
       </c>
     </row>
     <row r="4">
@@ -1794,34 +1794,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E4" t="n">
-        <v>13021.399</v>
+        <v>13256.738</v>
       </c>
       <c r="F4" t="n">
-        <v>38306.329</v>
+        <v>38113.516</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>308.006</v>
+        <v>265.027</v>
       </c>
       <c r="I4" t="n">
-        <v>1841.35</v>
+        <v>1796</v>
       </c>
       <c r="J4" t="n">
-        <v>6944.626</v>
+        <v>7336.804</v>
       </c>
       <c r="K4" t="n">
         <v>567647</v>
       </c>
       <c r="L4" t="n">
-        <v>5.97</v>
+        <v>5.761</v>
       </c>
       <c r="M4" t="n">
-        <v>6.78</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="5">
@@ -1841,34 +1841,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E5" t="n">
-        <v>232.93</v>
+        <v>241.99</v>
       </c>
       <c r="F5" t="n">
-        <v>880.566</v>
+        <v>902.081</v>
       </c>
       <c r="G5" t="n">
         <v>-1711</v>
       </c>
       <c r="H5" t="n">
-        <v>4.535</v>
+        <v>3.968</v>
       </c>
       <c r="I5" t="n">
-        <v>23.849</v>
+        <v>23.779</v>
       </c>
       <c r="J5" t="n">
-        <v>93.53100000000001</v>
+        <v>100.137</v>
       </c>
       <c r="K5" t="n">
         <v>18549</v>
       </c>
       <c r="L5" t="n">
-        <v>9.457000000000001</v>
+        <v>9.244999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>9.125999999999999</v>
+        <v>4.495</v>
       </c>
     </row>
     <row r="6">
@@ -1888,34 +1888,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E6" t="n">
-        <v>868.915</v>
+        <v>884.1799999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>2532.877</v>
+        <v>2580.693</v>
       </c>
       <c r="G6" t="n">
         <v>-2234</v>
       </c>
       <c r="H6" t="n">
-        <v>58.44</v>
+        <v>52.834</v>
       </c>
       <c r="I6" t="n">
-        <v>177.395</v>
+        <v>174.8</v>
       </c>
       <c r="J6" t="n">
-        <v>442.594</v>
+        <v>466.512</v>
       </c>
       <c r="K6" t="n">
         <v>34296</v>
       </c>
       <c r="L6" t="n">
-        <v>6.404</v>
+        <v>6.343</v>
       </c>
       <c r="M6" t="n">
-        <v>4.972</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="7">
@@ -1935,34 +1935,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E7" t="n">
-        <v>1.986</v>
+        <v>2.004</v>
       </c>
       <c r="F7" t="n">
-        <v>1.892</v>
+        <v>1.941</v>
       </c>
       <c r="G7" t="n">
         <v>-62.425</v>
       </c>
       <c r="H7" t="n">
-        <v>1.188</v>
+        <v>1.163</v>
       </c>
       <c r="I7" t="n">
-        <v>1.675</v>
+        <v>1.683</v>
       </c>
       <c r="J7" t="n">
-        <v>2.525</v>
+        <v>2.6</v>
       </c>
       <c r="K7" t="n">
         <v>22.725</v>
       </c>
       <c r="L7" t="n">
-        <v>-6.664</v>
+        <v>-6.537</v>
       </c>
       <c r="M7" t="n">
-        <v>4.972</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="8">
@@ -1982,34 +1982,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E8" t="n">
-        <v>1595.566</v>
+        <v>1634.082</v>
       </c>
       <c r="F8" t="n">
-        <v>4570.529</v>
+        <v>4671.846</v>
       </c>
       <c r="G8" t="n">
         <v>-3338</v>
       </c>
       <c r="H8" t="n">
-        <v>117.547</v>
+        <v>110.155</v>
       </c>
       <c r="I8" t="n">
-        <v>339.003</v>
+        <v>335.73</v>
       </c>
       <c r="J8" t="n">
-        <v>848.096</v>
+        <v>892.597</v>
       </c>
       <c r="K8" t="n">
         <v>50321</v>
       </c>
       <c r="L8" t="n">
-        <v>5.871</v>
+        <v>5.766</v>
       </c>
       <c r="M8" t="n">
-        <v>4.671</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="9">
@@ -2029,34 +2029,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4623</v>
+        <v>4402</v>
       </c>
       <c r="E9" t="n">
-        <v>0.417</v>
+        <v>0.386</v>
       </c>
       <c r="F9" t="n">
-        <v>3.126</v>
+        <v>2.866</v>
       </c>
       <c r="G9" t="n">
         <v>-76.48</v>
       </c>
       <c r="H9" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="I9" t="n">
-        <v>0.52</v>
+        <v>0.523</v>
       </c>
       <c r="J9" t="n">
-        <v>0.959</v>
+        <v>0.946</v>
       </c>
       <c r="K9" t="n">
-        <v>54.395</v>
+        <v>23.572</v>
       </c>
       <c r="L9" t="n">
-        <v>-7.798</v>
+        <v>-12.171</v>
       </c>
       <c r="M9" t="n">
-        <v>0.495</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="10">
@@ -2076,34 +2076,34 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4599</v>
+        <v>4384</v>
       </c>
       <c r="E10" t="n">
-        <v>3.275</v>
+        <v>3.687</v>
       </c>
       <c r="F10" t="n">
-        <v>32.703</v>
+        <v>27.948</v>
       </c>
       <c r="G10" t="n">
-        <v>-914.7859999999999</v>
+        <v>-845.864</v>
       </c>
       <c r="H10" t="n">
-        <v>3.106</v>
+        <v>3.27</v>
       </c>
       <c r="I10" t="n">
-        <v>6.073</v>
+        <v>6.104</v>
       </c>
       <c r="J10" t="n">
-        <v>10.45</v>
+        <v>10.469</v>
       </c>
       <c r="K10" t="n">
-        <v>349.958</v>
+        <v>98.907</v>
       </c>
       <c r="L10" t="n">
-        <v>-14.173</v>
+        <v>-14.414</v>
       </c>
       <c r="M10" t="n">
-        <v>1.012</v>
+        <v>0.477</v>
       </c>
     </row>
     <row r="11">
@@ -2123,34 +2123,34 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E11" t="n">
-        <v>27016.492</v>
+        <v>27570.343</v>
       </c>
       <c r="F11" t="n">
-        <v>73988.75900000001</v>
+        <v>75332.40300000001</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1670.193</v>
+        <v>1533.647</v>
       </c>
       <c r="I11" t="n">
-        <v>4428.95</v>
+        <v>4396.682</v>
       </c>
       <c r="J11" t="n">
-        <v>14358.415</v>
+        <v>15104.469</v>
       </c>
       <c r="K11" t="n">
         <v>763595</v>
       </c>
       <c r="L11" t="n">
-        <v>5.133</v>
+        <v>5.077</v>
       </c>
       <c r="M11" t="n">
-        <v>6.285</v>
+        <v>1.748</v>
       </c>
     </row>
     <row r="12">
@@ -2170,34 +2170,34 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E12" t="n">
-        <v>0.101</v>
+        <v>0.102</v>
       </c>
       <c r="F12" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.12</v>
+        <v>0.122</v>
       </c>
       <c r="K12" t="n">
         <v>0.956</v>
       </c>
       <c r="L12" t="n">
-        <v>4.938</v>
+        <v>4.816</v>
       </c>
       <c r="M12" t="n">
-        <v>4.994</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="13">
@@ -2217,34 +2217,34 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4645</v>
+        <v>4404</v>
       </c>
       <c r="E13" t="n">
-        <v>9.176</v>
+        <v>9.315</v>
       </c>
       <c r="F13" t="n">
-        <v>2.205</v>
+        <v>2.005</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.127</v>
+        <v>1.361</v>
       </c>
       <c r="H13" t="n">
-        <v>7.907</v>
+        <v>8.083</v>
       </c>
       <c r="I13" t="n">
-        <v>9.218</v>
+        <v>9.266</v>
       </c>
       <c r="J13" t="n">
-        <v>10.418</v>
+        <v>10.435</v>
       </c>
       <c r="K13" t="n">
         <v>14.605</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.283</v>
+        <v>0.04</v>
       </c>
       <c r="M13" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="14">
@@ -2264,34 +2264,34 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E14" t="n">
-        <v>0.606</v>
+        <v>0.604</v>
       </c>
       <c r="F14" t="n">
-        <v>0.279</v>
+        <v>0.286</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.493</v>
+        <v>0.478</v>
       </c>
       <c r="I14" t="n">
         <v>0.661</v>
       </c>
       <c r="J14" t="n">
-        <v>0.765</v>
+        <v>0.769</v>
       </c>
       <c r="K14" t="n">
         <v>8.943</v>
       </c>
       <c r="L14" t="n">
-        <v>7.137</v>
+        <v>7.032</v>
       </c>
       <c r="M14" t="n">
-        <v>5.166</v>
+        <v>0.454</v>
       </c>
     </row>
     <row r="15">
@@ -2311,34 +2311,34 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E15" t="n">
-        <v>1.395</v>
+        <v>1.406</v>
       </c>
       <c r="F15" t="n">
-        <v>0.912</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.855</v>
+        <v>0.838</v>
       </c>
       <c r="I15" t="n">
-        <v>1.173</v>
+        <v>1.172</v>
       </c>
       <c r="J15" t="n">
-        <v>1.607</v>
+        <v>1.66</v>
       </c>
       <c r="K15" t="n">
         <v>4.979</v>
       </c>
       <c r="L15" t="n">
-        <v>1.485</v>
+        <v>1.418</v>
       </c>
       <c r="M15" t="n">
-        <v>10.095</v>
+        <v>5.653</v>
       </c>
     </row>
     <row r="16">
@@ -2358,34 +2358,34 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.25</v>
+        <v>0.255</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.362</v>
+        <v>0.352</v>
       </c>
       <c r="I16" t="n">
-        <v>0.593</v>
+        <v>0.596</v>
       </c>
       <c r="J16" t="n">
-        <v>0.763</v>
+        <v>0.772</v>
       </c>
       <c r="K16" t="n">
         <v>0.999</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.316</v>
+        <v>-0.293</v>
       </c>
       <c r="M16" t="n">
-        <v>6.285</v>
+        <v>1.748</v>
       </c>
     </row>
     <row r="17">
@@ -2405,34 +2405,34 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="E17" t="n">
-        <v>13.934</v>
+        <v>13.951</v>
       </c>
       <c r="F17" t="n">
-        <v>9.228999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="G17" t="n">
         <v>1.046</v>
       </c>
       <c r="H17" t="n">
-        <v>8.363</v>
+        <v>8.192</v>
       </c>
       <c r="I17" t="n">
-        <v>11.574</v>
+        <v>11.549</v>
       </c>
       <c r="J17" t="n">
-        <v>16.323</v>
+        <v>16.628</v>
       </c>
       <c r="K17" t="n">
         <v>99.232</v>
       </c>
       <c r="L17" t="n">
-        <v>2.736</v>
+        <v>2.643</v>
       </c>
       <c r="M17" t="n">
-        <v>5.273</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="18">
@@ -2452,31 +2452,31 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4640</v>
+        <v>4399</v>
       </c>
       <c r="E18" t="n">
-        <v>7.139</v>
+        <v>7.117</v>
       </c>
       <c r="F18" t="n">
-        <v>2.495</v>
+        <v>2.554</v>
       </c>
       <c r="G18" t="n">
         <v>-4.343</v>
       </c>
       <c r="H18" t="n">
-        <v>5.907</v>
+        <v>5.755</v>
       </c>
       <c r="I18" t="n">
-        <v>7.327</v>
+        <v>7.318</v>
       </c>
       <c r="J18" t="n">
-        <v>8.429</v>
+        <v>8.493</v>
       </c>
       <c r="K18" t="n">
         <v>18.461</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.496</v>
+        <v>-0.469</v>
       </c>
       <c r="M18" t="n">
         <v>8.673999999999999</v>
@@ -2499,31 +2499,31 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E19" t="n">
-        <v>1.983</v>
+        <v>1.957</v>
       </c>
       <c r="F19" t="n">
-        <v>3.948</v>
+        <v>3.97</v>
       </c>
       <c r="G19" t="n">
         <v>-16.04</v>
       </c>
       <c r="H19" t="n">
-        <v>0.648</v>
+        <v>0.548</v>
       </c>
       <c r="I19" t="n">
-        <v>2.149</v>
+        <v>2.121</v>
       </c>
       <c r="J19" t="n">
-        <v>3.765</v>
+        <v>3.762</v>
       </c>
       <c r="K19" t="n">
         <v>24.616</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.277</v>
+        <v>-0.26</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2546,31 +2546,31 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E20" t="n">
-        <v>2.147</v>
+        <v>2.148</v>
       </c>
       <c r="F20" t="n">
-        <v>2.178</v>
+        <v>2.192</v>
       </c>
       <c r="G20" t="n">
         <v>-1.676</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>1.862</v>
+        <v>1.867</v>
       </c>
       <c r="J20" t="n">
-        <v>3.07</v>
+        <v>3.118</v>
       </c>
       <c r="K20" t="n">
         <v>15.253</v>
       </c>
       <c r="L20" t="n">
-        <v>1.783</v>
+        <v>1.774</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2593,31 +2593,31 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E21" t="n">
-        <v>9.367000000000001</v>
+        <v>9.375</v>
       </c>
       <c r="F21" t="n">
-        <v>4.5</v>
+        <v>4.529</v>
       </c>
       <c r="G21" t="n">
         <v>2.65</v>
       </c>
       <c r="H21" t="n">
-        <v>6.325</v>
+        <v>6.269</v>
       </c>
       <c r="I21" t="n">
         <v>8.324</v>
       </c>
       <c r="J21" t="n">
-        <v>10.718</v>
+        <v>10.737</v>
       </c>
       <c r="K21" t="n">
         <v>27.475</v>
       </c>
       <c r="L21" t="n">
-        <v>1.594</v>
+        <v>1.583</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2640,31 +2640,31 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.671</v>
+        <v>-0.699</v>
       </c>
       <c r="F22" t="n">
-        <v>5.787</v>
+        <v>5.785</v>
       </c>
       <c r="G22" t="n">
         <v>-23.892</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.318</v>
+        <v>-3.264</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.032</v>
+        <v>-0.081</v>
       </c>
       <c r="J22" t="n">
-        <v>2.958</v>
+        <v>2.875</v>
       </c>
       <c r="K22" t="n">
         <v>8.907</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.988</v>
+        <v>-1.001</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2687,31 +2687,31 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E23" t="n">
-        <v>101.744</v>
+        <v>101.646</v>
       </c>
       <c r="F23" t="n">
-        <v>7.833</v>
+        <v>7.755</v>
       </c>
       <c r="G23" t="n">
         <v>75.367</v>
       </c>
       <c r="H23" t="n">
-        <v>97.798</v>
+        <v>97.782</v>
       </c>
       <c r="I23" t="n">
-        <v>101.089</v>
+        <v>100.959</v>
       </c>
       <c r="J23" t="n">
-        <v>105.264</v>
+        <v>105.246</v>
       </c>
       <c r="K23" t="n">
         <v>127.329</v>
       </c>
       <c r="L23" t="n">
-        <v>0.266</v>
+        <v>0.209</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2734,31 +2734,31 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E24" t="n">
-        <v>8.847</v>
+        <v>8.849</v>
       </c>
       <c r="F24" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="G24" t="n">
         <v>1.205</v>
       </c>
       <c r="H24" t="n">
-        <v>8.002000000000001</v>
+        <v>7.98</v>
       </c>
       <c r="I24" t="n">
-        <v>9.183999999999999</v>
+        <v>9.186</v>
       </c>
       <c r="J24" t="n">
-        <v>10.473</v>
+        <v>10.48</v>
       </c>
       <c r="K24" t="n">
         <v>11.895</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.103</v>
+        <v>-1.102</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2781,31 +2781,31 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E25" t="n">
-        <v>5.442</v>
+        <v>5.431</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4</v>
+        <v>1.407</v>
       </c>
       <c r="G25" t="n">
         <v>2.648</v>
       </c>
       <c r="H25" t="n">
-        <v>4.092</v>
+        <v>4.09</v>
       </c>
       <c r="I25" t="n">
-        <v>5.471</v>
+        <v>5.466</v>
       </c>
       <c r="J25" t="n">
-        <v>6.243</v>
+        <v>6.23</v>
       </c>
       <c r="K25" t="n">
         <v>8.286</v>
       </c>
       <c r="L25" t="n">
-        <v>0.173</v>
+        <v>0.191</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -2828,31 +2828,31 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="E26" t="n">
-        <v>85.48099999999999</v>
+        <v>85.422</v>
       </c>
       <c r="F26" t="n">
-        <v>38.213</v>
+        <v>38.408</v>
       </c>
       <c r="G26" t="n">
         <v>20.058</v>
       </c>
       <c r="H26" t="n">
-        <v>53.573</v>
+        <v>53.22</v>
       </c>
       <c r="I26" t="n">
-        <v>83.316</v>
+        <v>83.249</v>
       </c>
       <c r="J26" t="n">
-        <v>105.124</v>
+        <v>105.025</v>
       </c>
       <c r="K26" t="n">
         <v>200.399</v>
       </c>
       <c r="L26" t="n">
-        <v>0.765</v>
+        <v>0.769</v>
       </c>
       <c r="M26" t="n">
         <v>6.29</v>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E27" t="n">
         <v>0.001</v>
@@ -2887,7 +2887,7 @@
         <v>-0.156</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.015</v>
+        <v>-0.014</v>
       </c>
       <c r="I27" t="n">
         <v>0.004</v>
@@ -2899,10 +2899,10 @@
         <v>0.176</v>
       </c>
       <c r="L27" t="n">
-        <v>0.659</v>
+        <v>0.65</v>
       </c>
       <c r="M27" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2922,19 +2922,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E28" t="n">
-        <v>0.273</v>
+        <v>0.27</v>
       </c>
       <c r="F28" t="n">
-        <v>2.693</v>
+        <v>2.685</v>
       </c>
       <c r="G28" t="n">
         <v>-0.997</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.053</v>
+        <v>-0.054</v>
       </c>
       <c r="I28" t="n">
         <v>0.034</v>
@@ -2946,21 +2946,21 @@
         <v>46.744</v>
       </c>
       <c r="L28" t="n">
-        <v>16.167</v>
+        <v>16.214</v>
       </c>
       <c r="M28" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nfa_g</t>
+          <t>nfa_gdp</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NFA growth</t>
+          <t>NFA change (% GDP)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2969,34 +2969,34 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E29" t="n">
-        <v>0.225</v>
+        <v>2.571</v>
       </c>
       <c r="F29" t="n">
-        <v>2.059</v>
+        <v>13.945</v>
       </c>
       <c r="G29" t="n">
-        <v>-11.349</v>
+        <v>-124.185</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.098</v>
+        <v>-1.65</v>
       </c>
       <c r="I29" t="n">
-        <v>0.06</v>
+        <v>1.384</v>
       </c>
       <c r="J29" t="n">
-        <v>0.258</v>
+        <v>5.104</v>
       </c>
       <c r="K29" t="n">
-        <v>24.163</v>
+        <v>135.932</v>
       </c>
       <c r="L29" t="n">
-        <v>6.299</v>
+        <v>1.187</v>
       </c>
       <c r="M29" t="n">
-        <v>13.43</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -3016,19 +3016,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E30" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="F30" t="n">
-        <v>0.089</v>
+        <v>0.09</v>
       </c>
       <c r="G30" t="n">
         <v>-0.346</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.034</v>
+        <v>-0.033</v>
       </c>
       <c r="I30" t="n">
         <v>0.008</v>
@@ -3040,10 +3040,10 @@
         <v>0.404</v>
       </c>
       <c r="L30" t="n">
-        <v>0.765</v>
+        <v>0.77</v>
       </c>
       <c r="M30" t="n">
-        <v>13.43</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -3063,31 +3063,31 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.517</v>
+        <v>-3.513</v>
       </c>
       <c r="F31" t="n">
-        <v>8.052</v>
+        <v>8.066000000000001</v>
       </c>
       <c r="G31" t="n">
         <v>-39.268</v>
       </c>
       <c r="H31" t="n">
-        <v>-6.619</v>
+        <v>-6.658</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.456</v>
+        <v>-2.445</v>
       </c>
       <c r="J31" t="n">
-        <v>1.417</v>
+        <v>1.421</v>
       </c>
       <c r="K31" t="n">
         <v>12.504</v>
       </c>
       <c r="L31" t="n">
-        <v>-1.262</v>
+        <v>-1.261</v>
       </c>
       <c r="M31" t="n">
         <v>21.71</v>
